--- a/data/historico/semana_324.xlsx
+++ b/data/historico/semana_324.xlsx
@@ -21008,7 +21008,7 @@
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>229 - R</t>
+          <t>972 - R</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
@@ -21028,47 +21028,47 @@
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>17543896</t>
+          <t>17457338</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>Rua NATAL</t>
+          <t>Rua JOÃO BORGES DE BARROS</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>364 - R</t>
+          <t>62 - 3 - TB</t>
         </is>
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>18/09/2026 16:12</t>
+          <t>15/09/2026 09:14</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t>18/09/2026 16:41</t>
+          <t>15/09/2026 09:43</t>
         </is>
       </c>
       <c r="J10" s="25" t="n">
@@ -21078,47 +21078,47 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>17457338</t>
+          <t>17543896</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>Rua JOÃO BORGES DE BARROS</t>
+          <t>Rua NATAL</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>62 - 3 - TB</t>
+          <t>364 - R</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>15/09/2026 09:14</t>
+          <t>18/09/2026 16:12</t>
         </is>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
-          <t>15/09/2026 09:43</t>
+          <t>18/09/2026 16:41</t>
         </is>
       </c>
       <c r="J11" s="25" t="n">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>17483813</t>
+          <t>17457357</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
@@ -21198,27 +21198,27 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua ALCIDES VAZ GUIMARÃES</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>173 - R</t>
+          <t>86 - R</t>
         </is>
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 09:25</t>
+          <t>15/09/2026 15:08</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 09:52</t>
+          <t>15/09/2026 15:35</t>
         </is>
       </c>
       <c r="J13" s="25" t="n">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>17483810</t>
+          <t>17483813</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr">
@@ -21258,17 +21258,17 @@
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>192 - R</t>
+          <t>173 - R</t>
         </is>
       </c>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 08:56</t>
+          <t>16/09/2026 09:25</t>
         </is>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 09:23</t>
+          <t>16/09/2026 09:52</t>
         </is>
       </c>
       <c r="J14" s="25" t="n">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>17457357</t>
+          <t>17483810</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
@@ -21298,27 +21298,27 @@
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>Rua ALCIDES VAZ GUIMARÃES</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>86 - R</t>
+          <t>192 - R</t>
         </is>
       </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>15/09/2026 15:08</t>
+          <t>16/09/2026 08:56</t>
         </is>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
-          <t>15/09/2026 15:35</t>
+          <t>16/09/2026 09:23</t>
         </is>
       </c>
       <c r="J15" s="25" t="n">
@@ -21328,7 +21328,7 @@
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -21338,37 +21338,37 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>17542074</t>
+          <t>17518623</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>Rua JORGE ROBERTO SALOMAO</t>
+          <t>Rua CORUMBA</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>01 - OU</t>
+          <t>41 - R</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>18/09/2026 15:19</t>
+          <t>17/09/2026 14:01</t>
         </is>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
-          <t>18/09/2026 15:45</t>
+          <t>17/09/2026 14:27</t>
         </is>
       </c>
       <c r="J16" s="25" t="n">
@@ -21378,7 +21378,7 @@
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -21388,37 +21388,37 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>17518623</t>
+          <t>17542074</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>Rua CORUMBA</t>
+          <t>Rua JORGE ROBERTO SALOMAO</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>41 - R</t>
+          <t>01 - OU</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>17/09/2026 14:01</t>
+          <t>18/09/2026 15:19</t>
         </is>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t>17/09/2026 14:27</t>
+          <t>18/09/2026 15:45</t>
         </is>
       </c>
       <c r="J17" s="25" t="n">
@@ -21678,47 +21678,47 @@
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>17512686</t>
+          <t>17485684</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>Rua EDVALDO CARPES</t>
+          <t>Rua PORTO ALEGRE</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>668 - OU</t>
+          <t>651 - R</t>
         </is>
       </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>17/09/2026 15:54</t>
+          <t>16/09/2026 09:51</t>
         </is>
       </c>
       <c r="I23" s="25" t="inlineStr">
         <is>
-          <t>17/09/2026 16:17</t>
+          <t>16/09/2026 10:14</t>
         </is>
       </c>
       <c r="J23" s="25" t="n">
@@ -21728,47 +21728,47 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>17483229</t>
+          <t>17512686</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>419 - CENTRO 5</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>Rua PEDRO CELESTINO</t>
+          <t>Rua EDVALDO CARPES</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>131 - 2 - C</t>
+          <t>668 - OU</t>
         </is>
       </c>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 09:47</t>
+          <t>17/09/2026 15:54</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 10:10</t>
+          <t>17/09/2026 16:17</t>
         </is>
       </c>
       <c r="J24" s="25" t="n">
@@ -21778,47 +21778,47 @@
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>17485684</t>
+          <t>17483229</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>419 - CENTRO 5</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>Rua PORTO ALEGRE</t>
+          <t>Rua PEDRO CELESTINO</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>651 - R</t>
+          <t>131 - 2 - C</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 09:51</t>
+          <t>16/09/2026 09:47</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
         <is>
-          <t>16/09/2026 10:14</t>
+          <t>16/09/2026 10:10</t>
         </is>
       </c>
       <c r="J25" s="25" t="n">

--- a/data/historico/semana_324.xlsx
+++ b/data/historico/semana_324.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$43</definedName>
   </definedNames>
@@ -5412,19 +5412,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (1 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (2 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5475,8 +5475,30 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>Teonilda Florentino Vieira</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D3"/>
+  <autoFilter ref="A2:D4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_324.xlsx
+++ b/data/historico/semana_324.xlsx
@@ -30,8 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$43</definedName>
   </definedNames>
@@ -5412,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5424,7 +5424,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (2 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (3 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
@@ -5497,8 +5497,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D4"/>
+  <autoFilter ref="A2:D5"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -8301,7 +8323,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>100</v>
@@ -15889,7 +15911,7 @@
       </c>
       <c r="C252" s="45" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D252" s="45" t="n">
@@ -15921,55 +15943,55 @@
       </c>
       <c r="C253" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D253" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F253" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H253" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="45" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B254" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C254" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D253" s="45" t="n">
+      <c r="D254" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E253" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F253" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G253" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H253" s="45" t="n">
+      <c r="E254" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="46" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B254" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C254" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D254" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E254" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F254" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G254" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H254" s="46" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="255">
@@ -15985,11 +16007,11 @@
       </c>
       <c r="C255" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D255" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E255" s="46" t="n">
         <v>0.3</v>
@@ -16001,7 +16023,7 @@
         <v>0.6</v>
       </c>
       <c r="H255" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="256">
@@ -16017,23 +16039,23 @@
       </c>
       <c r="C256" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D256" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F256" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G256" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H256" s="46" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="257">
@@ -23076,7 +23098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23091,7 +23113,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (66 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (64 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -24329,327 +24351,327 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="n">
+      <c r="A37" s="34" t="n">
         <v>2951</v>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E37" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G37" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="n">
+      <c r="A38" s="34" t="n">
         <v>2918</v>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="D38" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E38" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G38" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="n">
+      <c r="A39" s="34" t="n">
         <v>120</v>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="D39" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="F39" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G39" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="n">
+      <c r="A40" s="34" t="n">
         <v>1936</v>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D40" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E40" s="35" t="inlineStr">
+      <c r="E40" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="F40" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G40" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="n">
+      <c r="A41" s="34" t="n">
         <v>1938</v>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="D41" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="E41" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F41" s="35" t="inlineStr">
+      <c r="F41" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G41" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G41" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="n">
+      <c r="A42" s="34" t="n">
         <v>2721</v>
       </c>
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D42" s="35" t="inlineStr">
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E42" s="35" t="inlineStr">
+      <c r="E42" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F42" s="35" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G42" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G42" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="n">
+      <c r="A43" s="34" t="n">
         <v>3038</v>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="C43" s="35" t="inlineStr">
+      <c r="C43" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D43" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="E43" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F43" s="35" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G43" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G43" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="n">
+      <c r="A44" s="34" t="n">
         <v>3128</v>
       </c>
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B44" s="34" t="inlineStr">
         <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="C44" s="35" t="inlineStr">
+      <c r="C44" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D44" s="35" t="inlineStr">
+      <c r="D44" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E44" s="35" t="inlineStr">
+      <c r="E44" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F44" s="35" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G44" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G44" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="n">
-        <v>113</v>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="C45" s="35" t="inlineStr">
+      <c r="A45" s="34" t="n">
+        <v>2951</v>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="E45" s="34" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F45" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G45" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="34" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
@@ -24680,31 +24702,31 @@
     </row>
     <row r="47">
       <c r="A47" s="34" t="n">
-        <v>1938</v>
+        <v>80</v>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G47" s="34" t="inlineStr">
@@ -24715,31 +24737,31 @@
     </row>
     <row r="48">
       <c r="A48" s="34" t="n">
-        <v>113</v>
+        <v>2789</v>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G48" s="34" t="inlineStr">
@@ -24750,11 +24772,11 @@
     </row>
     <row r="49">
       <c r="A49" s="34" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -24785,11 +24807,11 @@
     </row>
     <row r="50">
       <c r="A50" s="34" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
@@ -24820,11 +24842,11 @@
     </row>
     <row r="51">
       <c r="A51" s="34" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
@@ -24855,11 +24877,11 @@
     </row>
     <row r="52">
       <c r="A52" s="34" t="n">
-        <v>1942</v>
+        <v>86</v>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
@@ -24890,11 +24912,11 @@
     </row>
     <row r="53">
       <c r="A53" s="34" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -24925,11 +24947,11 @@
     </row>
     <row r="54">
       <c r="A54" s="34" t="n">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -24939,12 +24961,12 @@
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
@@ -24960,11 +24982,11 @@
     </row>
     <row r="55">
       <c r="A55" s="34" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
@@ -24974,102 +24996,102 @@
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="n">
-        <v>149</v>
-      </c>
-      <c r="B56" s="34" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="C56" s="34" t="inlineStr">
+      <c r="G56" s="35" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="n">
+        <v>80</v>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="E56" s="34" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F56" s="34" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G56" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n">
-        <v>149</v>
-      </c>
-      <c r="B57" s="34" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D57" s="34" t="inlineStr">
-        <is>
-          <t>17/09/2026</t>
-        </is>
-      </c>
-      <c r="E57" s="34" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F57" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G57" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="G57" s="35" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="35" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B58" s="35" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C58" s="35" t="inlineStr">
@@ -25100,11 +25122,11 @@
     </row>
     <row r="59">
       <c r="A59" s="35" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B59" s="35" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C59" s="35" t="inlineStr">
@@ -25135,11 +25157,11 @@
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
-        <v>1943</v>
+        <v>149</v>
       </c>
       <c r="B60" s="35" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C60" s="35" t="inlineStr">
@@ -25170,11 +25192,11 @@
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B61" s="35" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C61" s="35" t="inlineStr">
@@ -25205,11 +25227,11 @@
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B62" s="35" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
@@ -25240,11 +25262,11 @@
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
-        <v>1942</v>
+        <v>161</v>
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
@@ -25275,11 +25297,11 @@
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
-        <v>124</v>
+        <v>1996</v>
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
@@ -25310,11 +25332,11 @@
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
@@ -25345,11 +25367,11 @@
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
@@ -25378,78 +25400,8 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="35" t="n">
-        <v>86</v>
-      </c>
-      <c r="B67" s="35" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C67" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D67" s="35" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="E67" s="35" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F67" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G67" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="35" t="n">
-        <v>157</v>
-      </c>
-      <c r="B68" s="35" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C68" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D68" s="35" t="inlineStr">
-        <is>
-          <t>18/09/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="35" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F68" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G68" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G68"/>
+  <autoFilter ref="A2:G66"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_324.xlsx
+++ b/data/historico/semana_324.xlsx
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
